--- a/data/trans_bre/KIDM_A_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/KIDM_A_R-Habitat-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 5,29</t>
+          <t>-6,13; 5,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 6,31</t>
+          <t>-5,91; 6,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,43; -1,09</t>
+          <t>-11,38; -1,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,19</t>
+          <t>0,0; 10,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 508,76</t>
+          <t>-100,0; 638,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 1,93</t>
+          <t>-5,3; 2,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 2,3</t>
+          <t>-7,25; 2,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 2,2</t>
+          <t>-3,37; 2,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 3,47</t>
+          <t>-4,32; 3,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 292,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-89,9; 106,81</t>
+          <t>-89,74; 136,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 3,5</t>
+          <t>-2,18; 3,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 4,61</t>
+          <t>-2,61; 5,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 9,35</t>
+          <t>-0,21; 9,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,72</t>
+          <t>0,0; 3,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 8,71</t>
+          <t>0,9; 7,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 4,55</t>
+          <t>-3,88; 6,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 2,35</t>
+          <t>-1,45; 2,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 4,07</t>
+          <t>-5,53; 3,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-85,9; 514,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 2,44</t>
+          <t>-1,41; 2,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 1,94</t>
+          <t>-2,99; 1,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 1,49</t>
+          <t>-1,84; 1,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 1,71</t>
+          <t>-1,92; 1,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-62,28; 238,28</t>
+          <t>-59,43; 223,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-58,81; 83,02</t>
+          <t>-62,01; 72,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-71,16; 184,35</t>
+          <t>-74,28; 166,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 318,49</t>
+          <t>-90,67; 389,1</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/KIDM_A_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/KIDM_A_R-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con salud general autopercibida regular o mala (autopercepción menor)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 5,21</t>
+          <t>-5,95; 4,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 6,34</t>
+          <t>-6,24; 6,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,38; -1,06</t>
+          <t>-11,42; -1,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,76</t>
+          <t>0,0; 11,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 638,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 2,29</t>
+          <t>-5,22; 2,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 2,32</t>
+          <t>-7,05; 2,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 2,27</t>
+          <t>-2,81; 2,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 3,82</t>
+          <t>-4,57; 3,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-89,74; 136,51</t>
+          <t>-87,05; 157,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 3,44</t>
+          <t>-2,18; 3,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 5,65</t>
+          <t>-2,68; 4,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 9,18</t>
+          <t>-0,23; 9,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,65</t>
+          <t>0,0; 4,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 7,79</t>
+          <t>0,9; 8,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 6,04</t>
+          <t>-4,32; 5,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 2,34</t>
+          <t>-1,46; 2,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 3,24</t>
+          <t>-5,3; 3,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-85,9; 514,34</t>
+          <t>-100,0; 433,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 2,33</t>
+          <t>-1,47; 2,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 1,87</t>
+          <t>-2,68; 2,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 1,36</t>
+          <t>-1,87; 1,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 1,75</t>
+          <t>-1,76; 1,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-59,43; 223,72</t>
+          <t>-58,76; 232,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-62,01; 72,51</t>
+          <t>-57,28; 84,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-74,28; 166,76</t>
+          <t>-74,95; 162,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-90,67; 389,1</t>
+          <t>-94,52; 466,48</t>
         </is>
       </c>
     </row>
